--- a/DOSSIES_MULTIFORMATO/FENIXSOFT/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FENIXSOFT/dossie.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,6 +1165,198 @@
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FENIXSOFT2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>001/2020</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>120028</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10/2020</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20.000,00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1967 dias</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FENIXSOFT2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>002/2020</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>120029</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10/2020</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>135.000,00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1967 dias</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FENIXSOFT2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>002/2020</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>120412</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11/2020</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>135.000,00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1942 dias</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FENIXSOFT2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>001/2020</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>121733</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>01/2021</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>300.000,00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1871 dias</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DOSSIES_MULTIFORMATO/FENIXSOFT/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FENIXSOFT/dossie.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2029-10-01</t>
+          <t>2027-02-28</t>
         </is>
       </c>
     </row>
